--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_cherrytalespine[Mod道具信息-CherryTaleSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_cherrytalespine[Mod道具信息-CherryTaleSpine].xlsx
@@ -5894,7 +5894,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:BeastHand_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:BeastHand_01</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData BeastHand_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData BeastHand_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Body_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Body_01</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Body_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Body_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Finished_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Finished_01</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Finished_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Finished_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Finishing_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Finishing_01</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Finishing_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Finishing_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Idle_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Idle_01</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Idle_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Idle_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Insert_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Insert_01</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Insert_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Insert_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_01</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_02</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_02</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_02 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_02 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_03</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManLeft_03</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_03 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManLeft_03 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_01</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_02</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_02</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_02 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_02 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_03</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:ManRight_03</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_03 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData ManRight_03 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Penis_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Penis_01</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Penis_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Penis_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Penis_02</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Penis_02</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Penis_02 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Penis_02 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Squirt_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Squirt_01</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Squirt_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Squirt_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|Mouth_01&amp;ui_show_idle_anim:Tail_01</t>
+          <t>ui_show_res:a009_03_SkeletonData&amp;ui_show_data:0.1604;0,0&amp;ui_show_skin:AEye_01|BEye_01|Mouth_01&amp;ui_show_idle_anim:Tail_01</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Tail_01 skin:AEye_01|Mouth_01)</t>
+          <t>樱桃幻化药(CherryTale a009_03 a009_03_SkeletonData Tail_01 skin:AEye_01|BEye_01|Mouth_01)</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -51782,7 +51782,7 @@
       <c r="I1069" t="inlineStr"/>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_01</t>
         </is>
       </c>
       <c r="K1069" t="n">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="L1069" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Finished_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Finished_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1069" t="inlineStr"/>
@@ -51830,7 +51830,7 @@
       <c r="I1070" t="inlineStr"/>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finishing_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finishing_01</t>
         </is>
       </c>
       <c r="K1070" t="n">
@@ -51838,7 +51838,7 @@
       </c>
       <c r="L1070" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Finishing_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Finishing_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1070" t="inlineStr"/>
@@ -51878,7 +51878,7 @@
       <c r="I1071" t="inlineStr"/>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Gwomanbody_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Gwomanbody_01</t>
         </is>
       </c>
       <c r="K1071" t="n">
@@ -51886,7 +51886,7 @@
       </c>
       <c r="L1071" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Gwomanbody_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Gwomanbody_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1071" t="inlineStr"/>
@@ -51926,7 +51926,7 @@
       <c r="I1072" t="inlineStr"/>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Hand_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Hand_01</t>
         </is>
       </c>
       <c r="K1072" t="n">
@@ -51934,7 +51934,7 @@
       </c>
       <c r="L1072" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Hand_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Hand_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1072" t="inlineStr"/>
@@ -51974,7 +51974,7 @@
       <c r="I1073" t="inlineStr"/>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Hwomanbody_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Hwomanbody_01</t>
         </is>
       </c>
       <c r="K1073" t="n">
@@ -51982,7 +51982,7 @@
       </c>
       <c r="L1073" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Hwomanbody_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Hwomanbody_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1073" t="inlineStr"/>
@@ -52022,7 +52022,7 @@
       <c r="I1074" t="inlineStr"/>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01</t>
         </is>
       </c>
       <c r="K1074" t="n">
@@ -52030,7 +52030,7 @@
       </c>
       <c r="L1074" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Idle_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Idle_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1074" t="inlineStr"/>
@@ -52070,7 +52070,7 @@
       <c r="I1075" t="inlineStr"/>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_01_G</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_01_G</t>
         </is>
       </c>
       <c r="K1075" t="n">
@@ -52078,7 +52078,7 @@
       </c>
       <c r="L1075" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Insert_01_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Insert_01_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1075" t="inlineStr"/>
@@ -52118,7 +52118,7 @@
       <c r="I1076" t="inlineStr"/>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_01_H</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_01_H</t>
         </is>
       </c>
       <c r="K1076" t="n">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="L1076" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Insert_01_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Insert_01_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1076" t="inlineStr"/>
@@ -52166,7 +52166,7 @@
       <c r="I1077" t="inlineStr"/>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:ManPenis_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:ManPenis_01</t>
         </is>
       </c>
       <c r="K1077" t="n">
@@ -52174,7 +52174,7 @@
       </c>
       <c r="L1077" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData ManPenis_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData ManPenis_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1077" t="inlineStr"/>
@@ -52214,7 +52214,7 @@
       <c r="I1078" t="inlineStr"/>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Manrighthand_03</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Manrighthand_03</t>
         </is>
       </c>
       <c r="K1078" t="n">
@@ -52222,7 +52222,7 @@
       </c>
       <c r="L1078" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Manrighthand_03 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Manrighthand_03 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1078" t="inlineStr"/>
@@ -52262,7 +52262,7 @@
       <c r="I1079" t="inlineStr"/>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen1_00</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen1_00</t>
         </is>
       </c>
       <c r="K1079" t="n">
@@ -52270,7 +52270,7 @@
       </c>
       <c r="L1079" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_00 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_00 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1079" t="inlineStr"/>
@@ -52310,7 +52310,7 @@
       <c r="I1080" t="inlineStr"/>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen1_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen1_01</t>
         </is>
       </c>
       <c r="K1080" t="n">
@@ -52318,7 +52318,7 @@
       </c>
       <c r="L1080" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1080" t="inlineStr"/>
@@ -52358,7 +52358,7 @@
       <c r="I1081" t="inlineStr"/>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen1_02</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen1_02</t>
         </is>
       </c>
       <c r="K1081" t="n">
@@ -52366,7 +52366,7 @@
       </c>
       <c r="L1081" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen1_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1081" t="inlineStr"/>
@@ -52406,7 +52406,7 @@
       <c r="I1082" t="inlineStr"/>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen2_00</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen2_00</t>
         </is>
       </c>
       <c r="K1082" t="n">
@@ -52414,7 +52414,7 @@
       </c>
       <c r="L1082" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_00 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_00 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1082" t="inlineStr"/>
@@ -52454,7 +52454,7 @@
       <c r="I1083" t="inlineStr"/>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen2_01</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen2_01</t>
         </is>
       </c>
       <c r="K1083" t="n">
@@ -52462,7 +52462,7 @@
       </c>
       <c r="L1083" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1083" t="inlineStr"/>
@@ -52502,7 +52502,7 @@
       <c r="I1084" t="inlineStr"/>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen2_02</t>
+          <t>ui_show_res:teaching_hcg01_SkeletonData&amp;ui_show_data:0.1644;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen2_02</t>
         </is>
       </c>
       <c r="K1084" t="n">
@@ -52510,7 +52510,7 @@
       </c>
       <c r="L1084" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg01 teaching_hcg01_SkeletonData Screen2_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1084" t="inlineStr"/>
@@ -52550,7 +52550,7 @@
       <c r="I1085" t="inlineStr"/>
       <c r="J1085" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_01_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_01_G</t>
         </is>
       </c>
       <c r="K1085" t="n">
@@ -52558,7 +52558,7 @@
       </c>
       <c r="L1085" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_01_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_01_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1085" t="inlineStr"/>
@@ -52598,7 +52598,7 @@
       <c r="I1086" t="inlineStr"/>
       <c r="J1086" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_01_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_01_H</t>
         </is>
       </c>
       <c r="K1086" t="n">
@@ -52606,7 +52606,7 @@
       </c>
       <c r="L1086" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_01_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_01_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1086" t="inlineStr"/>
@@ -52646,7 +52646,7 @@
       <c r="I1087" t="inlineStr"/>
       <c r="J1087" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_02_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_02_G</t>
         </is>
       </c>
       <c r="K1087" t="n">
@@ -52654,7 +52654,7 @@
       </c>
       <c r="L1087" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_02_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_02_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1087" t="inlineStr"/>
@@ -52694,7 +52694,7 @@
       <c r="I1088" t="inlineStr"/>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_02_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_02_H</t>
         </is>
       </c>
       <c r="K1088" t="n">
@@ -52702,7 +52702,7 @@
       </c>
       <c r="L1088" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_02_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_02_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1088" t="inlineStr"/>
@@ -52742,7 +52742,7 @@
       <c r="I1089" t="inlineStr"/>
       <c r="J1089" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finished_03_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finished_03_H</t>
         </is>
       </c>
       <c r="K1089" t="n">
@@ -52750,7 +52750,7 @@
       </c>
       <c r="L1089" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_03_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finished_03_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1089" t="inlineStr"/>
@@ -52790,7 +52790,7 @@
       <c r="I1090" t="inlineStr"/>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finishing_01_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finishing_01_G</t>
         </is>
       </c>
       <c r="K1090" t="n">
@@ -52798,7 +52798,7 @@
       </c>
       <c r="L1090" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_01_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_01_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1090" t="inlineStr"/>
@@ -52838,7 +52838,7 @@
       <c r="I1091" t="inlineStr"/>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finishing_01_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finishing_01_H</t>
         </is>
       </c>
       <c r="K1091" t="n">
@@ -52846,7 +52846,7 @@
       </c>
       <c r="L1091" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_01_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_01_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1091" t="inlineStr"/>
@@ -52886,7 +52886,7 @@
       <c r="I1092" t="inlineStr"/>
       <c r="J1092" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Finishing_02_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Finishing_02_G</t>
         </is>
       </c>
       <c r="K1092" t="n">
@@ -52894,7 +52894,7 @@
       </c>
       <c r="L1092" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_02_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Finishing_02_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1092" t="inlineStr"/>
@@ -52934,7 +52934,7 @@
       <c r="I1093" t="inlineStr"/>
       <c r="J1093" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:GBody_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:GBody_01</t>
         </is>
       </c>
       <c r="K1093" t="n">
@@ -52942,7 +52942,7 @@
       </c>
       <c r="L1093" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GBody_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GBody_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1093" t="inlineStr"/>
@@ -52982,7 +52982,7 @@
       <c r="I1094" t="inlineStr"/>
       <c r="J1094" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:GPussyblush_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:GPussyblush_01</t>
         </is>
       </c>
       <c r="K1094" t="n">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="L1094" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GPussyblush_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GPussyblush_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1094" t="inlineStr"/>
@@ -53030,7 +53030,7 @@
       <c r="I1095" t="inlineStr"/>
       <c r="J1095" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:GWater_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:GWater_01</t>
         </is>
       </c>
       <c r="K1095" t="n">
@@ -53038,7 +53038,7 @@
       </c>
       <c r="L1095" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GWater_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData GWater_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1095" t="inlineStr"/>
@@ -53078,7 +53078,7 @@
       <c r="I1096" t="inlineStr"/>
       <c r="J1096" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:HBody_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:HBody_01</t>
         </is>
       </c>
       <c r="K1096" t="n">
@@ -53086,7 +53086,7 @@
       </c>
       <c r="L1096" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HBody_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HBody_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1096" t="inlineStr"/>
@@ -53126,7 +53126,7 @@
       <c r="I1097" t="inlineStr"/>
       <c r="J1097" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:HBody_02</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:HBody_02</t>
         </is>
       </c>
       <c r="K1097" t="n">
@@ -53134,7 +53134,7 @@
       </c>
       <c r="L1097" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HBody_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HBody_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1097" t="inlineStr"/>
@@ -53174,7 +53174,7 @@
       <c r="I1098" t="inlineStr"/>
       <c r="J1098" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:HButtblush_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:HButtblush_01</t>
         </is>
       </c>
       <c r="K1098" t="n">
@@ -53182,7 +53182,7 @@
       </c>
       <c r="L1098" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HButtblush_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HButtblush_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1098" t="inlineStr"/>
@@ -53222,7 +53222,7 @@
       <c r="I1099" t="inlineStr"/>
       <c r="J1099" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:HWater_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:HWater_01</t>
         </is>
       </c>
       <c r="K1099" t="n">
@@ -53230,7 +53230,7 @@
       </c>
       <c r="L1099" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HWater_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData HWater_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1099" t="inlineStr"/>
@@ -53270,7 +53270,7 @@
       <c r="I1100" t="inlineStr"/>
       <c r="J1100" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Hnliquid_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Hnliquid_01</t>
         </is>
       </c>
       <c r="K1100" t="n">
@@ -53278,7 +53278,7 @@
       </c>
       <c r="L1100" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Hnliquid_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Hnliquid_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1100" t="inlineStr"/>
@@ -53318,7 +53318,7 @@
       <c r="I1101" t="inlineStr"/>
       <c r="J1101" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Hnliquid_02</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Hnliquid_02</t>
         </is>
       </c>
       <c r="K1101" t="n">
@@ -53326,7 +53326,7 @@
       </c>
       <c r="L1101" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Hnliquid_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Hnliquid_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1101" t="inlineStr"/>
@@ -53366,7 +53366,7 @@
       <c r="I1102" t="inlineStr"/>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01_1_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01_1_G</t>
         </is>
       </c>
       <c r="K1102" t="n">
@@ -53374,7 +53374,7 @@
       </c>
       <c r="L1102" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_1_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_1_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1102" t="inlineStr"/>
@@ -53414,7 +53414,7 @@
       <c r="I1103" t="inlineStr"/>
       <c r="J1103" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01_2_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01_2_G</t>
         </is>
       </c>
       <c r="K1103" t="n">
@@ -53422,7 +53422,7 @@
       </c>
       <c r="L1103" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_2_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_2_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1103" t="inlineStr"/>
@@ -53462,7 +53462,7 @@
       <c r="I1104" t="inlineStr"/>
       <c r="J1104" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01_3_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01_3_G</t>
         </is>
       </c>
       <c r="K1104" t="n">
@@ -53470,7 +53470,7 @@
       </c>
       <c r="L1104" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_3_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_3_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1104" t="inlineStr"/>
@@ -53510,7 +53510,7 @@
       <c r="I1105" t="inlineStr"/>
       <c r="J1105" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01_G</t>
         </is>
       </c>
       <c r="K1105" t="n">
@@ -53518,7 +53518,7 @@
       </c>
       <c r="L1105" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1105" t="inlineStr"/>
@@ -53558,7 +53558,7 @@
       <c r="I1106" t="inlineStr"/>
       <c r="J1106" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_01_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_01_H</t>
         </is>
       </c>
       <c r="K1106" t="n">
@@ -53566,7 +53566,7 @@
       </c>
       <c r="L1106" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_01_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1106" t="inlineStr"/>
@@ -53606,7 +53606,7 @@
       <c r="I1107" t="inlineStr"/>
       <c r="J1107" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_02_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_02_G</t>
         </is>
       </c>
       <c r="K1107" t="n">
@@ -53614,7 +53614,7 @@
       </c>
       <c r="L1107" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_02_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_02_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1107" t="inlineStr"/>
@@ -53654,7 +53654,7 @@
       <c r="I1108" t="inlineStr"/>
       <c r="J1108" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_02_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_02_H</t>
         </is>
       </c>
       <c r="K1108" t="n">
@@ -53662,7 +53662,7 @@
       </c>
       <c r="L1108" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_02_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_02_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1108" t="inlineStr"/>
@@ -53702,7 +53702,7 @@
       <c r="I1109" t="inlineStr"/>
       <c r="J1109" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Idle_03_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Idle_03_H</t>
         </is>
       </c>
       <c r="K1109" t="n">
@@ -53710,7 +53710,7 @@
       </c>
       <c r="L1109" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_03_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Idle_03_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1109" t="inlineStr"/>
@@ -53750,7 +53750,7 @@
       <c r="I1110" t="inlineStr"/>
       <c r="J1110" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_01_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_01_G</t>
         </is>
       </c>
       <c r="K1110" t="n">
@@ -53758,7 +53758,7 @@
       </c>
       <c r="L1110" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_01_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_01_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1110" t="inlineStr"/>
@@ -53798,7 +53798,7 @@
       <c r="I1111" t="inlineStr"/>
       <c r="J1111" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_01_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_01_H</t>
         </is>
       </c>
       <c r="K1111" t="n">
@@ -53806,7 +53806,7 @@
       </c>
       <c r="L1111" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_01_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_01_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1111" t="inlineStr"/>
@@ -53846,7 +53846,7 @@
       <c r="I1112" t="inlineStr"/>
       <c r="J1112" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_02_G</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_02_G</t>
         </is>
       </c>
       <c r="K1112" t="n">
@@ -53854,7 +53854,7 @@
       </c>
       <c r="L1112" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_02_G skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_02_G skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1112" t="inlineStr"/>
@@ -53894,7 +53894,7 @@
       <c r="I1113" t="inlineStr"/>
       <c r="J1113" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Insert_02_H</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Insert_02_H</t>
         </is>
       </c>
       <c r="K1113" t="n">
@@ -53902,7 +53902,7 @@
       </c>
       <c r="L1113" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_02_H skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Insert_02_H skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1113" t="inlineStr"/>
@@ -53942,7 +53942,7 @@
       <c r="I1114" t="inlineStr"/>
       <c r="J1114" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:ManHand_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:ManHand_01</t>
         </is>
       </c>
       <c r="K1114" t="n">
@@ -53950,7 +53950,7 @@
       </c>
       <c r="L1114" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1114" t="inlineStr"/>
@@ -53990,7 +53990,7 @@
       <c r="I1115" t="inlineStr"/>
       <c r="J1115" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:ManHand_02</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:ManHand_02</t>
         </is>
       </c>
       <c r="K1115" t="n">
@@ -53998,7 +53998,7 @@
       </c>
       <c r="L1115" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1115" t="inlineStr"/>
@@ -54038,7 +54038,7 @@
       <c r="I1116" t="inlineStr"/>
       <c r="J1116" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:ManHand_03</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:ManHand_03</t>
         </is>
       </c>
       <c r="K1116" t="n">
@@ -54046,7 +54046,7 @@
       </c>
       <c r="L1116" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_03 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData ManHand_03 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1116" t="inlineStr"/>
@@ -54086,7 +54086,7 @@
       <c r="I1117" t="inlineStr"/>
       <c r="J1117" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen1_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen1_01</t>
         </is>
       </c>
       <c r="K1117" t="n">
@@ -54094,7 +54094,7 @@
       </c>
       <c r="L1117" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen1_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen1_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1117" t="inlineStr"/>
@@ -54134,7 +54134,7 @@
       <c r="I1118" t="inlineStr"/>
       <c r="J1118" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen1_02</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen1_02</t>
         </is>
       </c>
       <c r="K1118" t="n">
@@ -54142,7 +54142,7 @@
       </c>
       <c r="L1118" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen1_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen1_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1118" t="inlineStr"/>
@@ -54182,7 +54182,7 @@
       <c r="I1119" t="inlineStr"/>
       <c r="J1119" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen2_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen2_01</t>
         </is>
       </c>
       <c r="K1119" t="n">
@@ -54190,7 +54190,7 @@
       </c>
       <c r="L1119" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen2_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen2_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1119" t="inlineStr"/>
@@ -54230,7 +54230,7 @@
       <c r="I1120" t="inlineStr"/>
       <c r="J1120" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen2_02</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen2_02</t>
         </is>
       </c>
       <c r="K1120" t="n">
@@ -54238,7 +54238,7 @@
       </c>
       <c r="L1120" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen2_02 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen2_02 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1120" t="inlineStr"/>
@@ -54278,7 +54278,7 @@
       <c r="I1121" t="inlineStr"/>
       <c r="J1121" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Screen_00</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Screen_00</t>
         </is>
       </c>
       <c r="K1121" t="n">
@@ -54286,7 +54286,7 @@
       </c>
       <c r="L1121" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen_00 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Screen_00 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1121" t="inlineStr"/>
@@ -54326,7 +54326,7 @@
       <c r="I1122" t="inlineStr"/>
       <c r="J1122" t="inlineStr">
         <is>
-          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|GMouth_01&amp;ui_show_idle_anim:Sweat_01</t>
+          <t>ui_show_res:teaching_hcg02_SkeletonData&amp;ui_show_data:0.1852;0,0&amp;ui_show_skin:GEye_01|HEye_01|GMouth_01|HMouth_01&amp;ui_show_idle_anim:Sweat_01</t>
         </is>
       </c>
       <c r="K1122" t="n">
@@ -54334,7 +54334,7 @@
       </c>
       <c r="L1122" t="inlineStr">
         <is>
-          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Sweat_01 skin:GEye_01|GMouth_01)</t>
+          <t>樱桃幻化药(CherryTale teaching_hcg02 teaching_hcg02_SkeletonData Sweat_01 skin:GEye_01|HEye_01|GMouth_01|HMouth_01)</t>
         </is>
       </c>
       <c r="M1122" t="inlineStr"/>
